--- a/Data/Building/TeaRoom.Humidity.xlsx
+++ b/Data/Building/TeaRoom.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709363076</v>
+        <v>1711934462</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,10 +502,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TeaRoom.Humidity.state: Moist</t>
+          <t>TeaRoom.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709869653</v>
+        <v>1711948608</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709938672</v>
+        <v>1712208386</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1710086409</v>
+        <v>1712549807</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TeaRoom.Humidity.state: ExcessivelyHumid</t>
+          <t>TeaRoom.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1710209272</v>
+        <v>1712642722</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1710225918</v>
+        <v>1712938493</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1710291995</v>
+        <v>1712970060</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1710481456</v>
+        <v>1713394605</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1710556227</v>
+        <v>1713495722</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1710738151</v>
+        <v>1713505941</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1711074107</v>
+        <v>1713756495</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1711260728</v>
+        <v>1713764319</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1711340987</v>
+        <v>1713838326</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1711511863</v>
+        <v>1714010676</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,40 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Humidity_Change</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1714093771</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>TeaRoom.Humidity.state: Moist</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
